--- a/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
+++ b/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#urn:oid:1.2.250.1.213.1.6.1.7</t>
+    <t>OID:1.2.250.1.213.1.6.1.7</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
+++ b/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
@@ -76,7 +76,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
+++ b/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="212">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-06-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>3410</t>
+  </si>
+  <si>
+    <t>Services d'incendie et de secours</t>
   </si>
   <si>
     <t>4101</t>
@@ -1017,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +2000,18 @@
       </c>
       <c r="D81" s="2"/>
     </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
+++ b/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20240628120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
+++ b/ig/main/CodeSystem-TRE-R65-AgregatCategorieEtablissement.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
